--- a/导入模板合集.xlsx
+++ b/导入模板合集.xlsx
@@ -401,25 +401,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>课程名称</v>
       </c>
       <c r="B1" t="str">
-        <v>教师</v>
+        <v>教师账号</v>
       </c>
       <c r="C1" t="str">
+        <v>教师姓名</v>
+      </c>
+      <c r="D1" t="str">
         <v>班级</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
+        <v>院系</v>
+      </c>
+      <c r="F1" t="str">
         <v>教室</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>日期</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>时间段</v>
       </c>
     </row>
@@ -428,91 +434,63 @@
         <v>React 前端开发实战</v>
       </c>
       <c r="B2" t="str">
+        <v>teacher-wang</v>
+      </c>
+      <c r="C2" t="str">
         <v>王老师</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>计算机2101班</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
+        <v>计算机学院</v>
+      </c>
+      <c r="F2" t="str">
         <v>A101</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>2026-09-01</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>09:00-11:00</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>React 前端开发实战</v>
+        <v>Python 数据分析</v>
       </c>
       <c r="B3" t="str">
-        <v>王老师</v>
+        <v>teacher-li</v>
       </c>
       <c r="C3" t="str">
-        <v>计算机2101班</v>
+        <v>李老师</v>
       </c>
       <c r="D3" t="str">
-        <v>A101</v>
+        <v>软件工程2101班</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-09-08</v>
+        <v>计算机学院</v>
       </c>
       <c r="F3" t="str">
-        <v>09:00-11:00</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Python 数据分析入门</v>
-      </c>
-      <c r="B4" t="str">
-        <v>李老师</v>
-      </c>
-      <c r="C4" t="str">
-        <v>软件工程2101班</v>
-      </c>
-      <c r="D4" t="str">
         <v>B202</v>
       </c>
-      <c r="E4" t="str">
+      <c r="G3" t="str">
         <v>2026-09-02</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H3" t="str">
         <v>14:00-16:00</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>机器学习基础</v>
-      </c>
-      <c r="B5" t="str">
-        <v>张老师</v>
-      </c>
-      <c r="C5" t="str">
-        <v>软件工程2102班</v>
-      </c>
-      <c r="D5" t="str">
-        <v>D401</v>
-      </c>
-      <c r="E5" t="str">
-        <v>2026-09-03</v>
-      </c>
-      <c r="F5" t="str">
-        <v>09:00-12:00</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,6 +502,9 @@
       <c r="C1" t="str">
         <v>学生学号</v>
       </c>
+      <c r="D1" t="str">
+        <v>院系</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -535,50 +516,34 @@
       <c r="C2" t="str">
         <v>S2024001</v>
       </c>
+      <c r="D2" t="str">
+        <v>计算机学院</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>计算机2101班</v>
+        <v>软件工程2101班</v>
       </c>
       <c r="B3" t="str">
-        <v>李华</v>
+        <v>王芳</v>
       </c>
       <c r="C3" t="str">
-        <v>S2024002</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>软件工程2101班</v>
-      </c>
-      <c r="B4" t="str">
-        <v>王芳</v>
-      </c>
-      <c r="C4" t="str">
         <v>S2024003</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>软件工程2101班</v>
-      </c>
-      <c r="B5" t="str">
-        <v>赵磊</v>
-      </c>
-      <c r="C5" t="str">
-        <v>S2024004</v>
+      <c r="D3" t="str">
+        <v>计算机学院</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -604,40 +569,16 @@
         <v>S2024002</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>王芳</v>
-      </c>
-      <c r="B4" t="str">
-        <v>S2024003</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>赵磊</v>
-      </c>
-      <c r="B5" t="str">
-        <v>S2024004</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>陈静</v>
-      </c>
-      <c r="B6" t="str">
-        <v>S2024005</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -663,32 +604,16 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>王芳</v>
-      </c>
-      <c r="B4">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>赵磊</v>
-      </c>
-      <c r="B5">
-        <v>80</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -700,9 +625,6 @@
       <c r="C1" t="str">
         <v>学生2</v>
       </c>
-      <c r="D1" t="str">
-        <v>学生3</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -714,41 +636,10 @@
       <c r="C2" t="str">
         <v>李华</v>
       </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>第二组</v>
-      </c>
-      <c r="B3" t="str">
-        <v>王芳</v>
-      </c>
-      <c r="C3" t="str">
-        <v>赵磊</v>
-      </c>
-      <c r="D3" t="str">
-        <v>陈静</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>第三组</v>
-      </c>
-      <c r="B4" t="str">
-        <v>刘洋</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>